--- a/data/trans_orig/P36B07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016</t>
+          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59790</t>
+          <t>59405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92520</t>
+          <t>90667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90092</t>
+          <t>88153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124002</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155339</t>
+          <t>157839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>205913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49406</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78116</t>
+          <t>78199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81619</t>
+          <t>80024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109657</t>
+          <t>108953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>151114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86420</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122894</t>
+          <t>123222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61767</t>
+          <t>62360</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91294</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155992</t>
+          <t>158751</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>203431</t>
+          <t>208300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68413</t>
+          <t>69383</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53324</t>
+          <t>54305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83212</t>
+          <t>85598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129678</t>
+          <t>131360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175200</t>
+          <t>174572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74110</t>
+          <t>73535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110395</t>
+          <t>108838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63688</t>
+          <t>62969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94881</t>
+          <t>94976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146110</t>
+          <t>146731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>192639</t>
+          <t>194358</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89389</t>
+          <t>90231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127994</t>
+          <t>128289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100101</t>
+          <t>99708</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>136602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200322</t>
+          <t>198560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254535</t>
+          <t>254654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93013</t>
+          <t>91444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131767</t>
+          <t>131667</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83362</t>
+          <t>83352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117166</t>
+          <t>117926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>186260</t>
+          <t>184999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235067</t>
+          <t>235620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122465</t>
+          <t>122734</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162513</t>
+          <t>164570</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97130</t>
+          <t>97172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135838</t>
+          <t>134385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230175</t>
+          <t>230050</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>287532</t>
+          <t>285515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102114</t>
+          <t>104393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141719</t>
+          <t>142888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,49 +1766,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>24,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>115481</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>97454</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>134800</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>20,66%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>24,12%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>115481</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>98631</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>133903</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>242</t>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213751</t>
+          <t>211893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>267098</t>
+          <t>265666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87907</t>
+          <t>85681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125210</t>
+          <t>123670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93213</t>
+          <t>93205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128381</t>
+          <t>131115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188466</t>
+          <t>187069</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242009</t>
+          <t>243112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132418</t>
+          <t>131743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176013</t>
+          <t>177742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92089</t>
+          <t>92620</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130910</t>
+          <t>130323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235298</t>
+          <t>237794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294808</t>
+          <t>294991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111170</t>
+          <t>111941</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153111</t>
+          <t>154223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93529</t>
+          <t>93889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132021</t>
+          <t>131955</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217560</t>
+          <t>214993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273578</t>
+          <t>273924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122319</t>
+          <t>123137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>165944</t>
+          <t>165068</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>138054</t>
+          <t>139390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>180678</t>
+          <t>183301</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>272361</t>
+          <t>270935</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329051</t>
+          <t>330681</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109313</t>
+          <t>107733</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149222</t>
+          <t>149105</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111451</t>
+          <t>111714</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152021</t>
+          <t>151962</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>230617</t>
+          <t>231943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>287879</t>
+          <t>288385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87353</t>
+          <t>88542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125460</t>
+          <t>126757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120258</t>
+          <t>121057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164262</t>
+          <t>163832</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219940</t>
+          <t>219828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278268</t>
+          <t>278437</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143848</t>
+          <t>146401</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190208</t>
+          <t>192694</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152139</t>
+          <t>150946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200707</t>
+          <t>199839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>308795</t>
+          <t>306800</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374804</t>
+          <t>374649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115724</t>
+          <t>116586</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159888</t>
+          <t>158553</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103987</t>
+          <t>102015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143646</t>
+          <t>141625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228105</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288517</t>
+          <t>289164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106323</t>
+          <t>103265</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>148761</t>
+          <t>144814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>103222</t>
+          <t>103299</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>144305</t>
+          <t>146345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>220602</t>
+          <t>220032</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>277024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78678</t>
+          <t>77489</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115934</t>
+          <t>117017</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97511</t>
+          <t>96813</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136943</t>
+          <t>137607</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186687</t>
+          <t>186136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240070</t>
+          <t>240720</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96153</t>
+          <t>95825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137004</t>
+          <t>138996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89600</t>
+          <t>91003</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127240</t>
+          <t>131664</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>196287</t>
+          <t>196714</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>253752</t>
+          <t>254878</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>109758</t>
+          <t>111558</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>153373</t>
+          <t>151165</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>97489</t>
+          <t>99462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>139126</t>
+          <t>138184</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>220648</t>
+          <t>219547</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>275779</t>
+          <t>276965</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72635</t>
+          <t>73309</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108820</t>
+          <t>108559</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82726</t>
+          <t>85938</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>123448</t>
+          <t>122635</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>167333</t>
+          <t>166200</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>220130</t>
+          <t>217689</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82857</t>
+          <t>83393</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119085</t>
+          <t>122291</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>92404</t>
+          <t>93300</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>130081</t>
+          <t>131271</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>185222</t>
+          <t>184857</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>237453</t>
+          <t>237484</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>66776</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>100116</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>58446</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92500</t>
+          <t>92312</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>133289</t>
+          <t>134513</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>179642</t>
+          <t>182639</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>54143</t>
+          <t>53852</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87334</t>
+          <t>85756</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>74138</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>109774</t>
+          <t>109726</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>136829</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>186101</t>
+          <t>186428</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>88185</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>122409</t>
+          <t>121436</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>81667</t>
+          <t>83164</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115983</t>
+          <t>115921</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>177780</t>
+          <t>176850</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>225926</t>
+          <t>225648</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50328</t>
+          <t>50834</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>80232</t>
+          <t>79502</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>56625</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>87593</t>
+          <t>86422</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>114503</t>
+          <t>113492</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>156240</t>
+          <t>155684</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>46237</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74717</t>
+          <t>74314</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>65947</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>97666</t>
+          <t>98902</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>118988</t>
+          <t>118061</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>163144</t>
+          <t>161258</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>43647</t>
+          <t>43375</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>69639</t>
+          <t>71421</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>73819</t>
+          <t>73530</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>97421</t>
+          <t>96225</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>137189</t>
+          <t>135739</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>37001</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>64292</t>
+          <t>64133</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>51123</t>
+          <t>53941</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>83719</t>
+          <t>83207</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>95649</t>
+          <t>100203</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>137960</t>
+          <t>138401</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>74971</t>
+          <t>73745</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>103893</t>
+          <t>102313</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>90138</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>133262</t>
+          <t>131753</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>175014</t>
+          <t>173696</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>224686</t>
+          <t>221738</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30051</t>
+          <t>31766</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>51025</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>51165</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>84661</t>
+          <t>84662</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>90905</t>
+          <t>89975</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>128502</t>
+          <t>130617</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>38336</t>
+          <t>37767</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>62402</t>
+          <t>60262</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>63761</t>
+          <t>63614</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>101748</t>
+          <t>100928</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>108501</t>
+          <t>109145</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>151045</t>
+          <t>152760</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>48660</t>
+          <t>48455</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>59426</t>
+          <t>60641</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>96744</t>
+          <t>96353</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>93268</t>
+          <t>95370</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>137371</t>
+          <t>138174</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>30516</t>
+          <t>29984</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>51458</t>
+          <t>51541</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>76518</t>
+          <t>77432</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>81706</t>
+          <t>81938</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>120018</t>
+          <t>121193</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>775499</t>
+          <t>776595</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>878716</t>
+          <t>876645</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>787647</t>
+          <t>783952</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>888042</t>
+          <t>884012</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1586906</t>
+          <t>1593063</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1726097</t>
+          <t>1726593</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>589303</t>
+          <t>591922</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>682242</t>
+          <t>683327</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>593346</t>
+          <t>590805</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>689326</t>
+          <t>686741</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1208315</t>
+          <t>1211457</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1336252</t>
+          <t>1336381</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>677767</t>
+          <t>672162</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>774753</t>
+          <t>770752</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>696186</t>
+          <t>699403</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>798057</t>
+          <t>796983</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1407294</t>
+          <t>1398045</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1542958</t>
+          <t>1537869</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>565913</t>
+          <t>563536</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>653903</t>
+          <t>655116</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>593804</t>
+          <t>593319</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>688247</t>
+          <t>685737</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1180480</t>
+          <t>1188773</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1311687</t>
+          <t>1323789</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>529160</t>
+          <t>531729</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>617529</t>
+          <t>622322</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>608648</t>
+          <t>609319</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>702763</t>
+          <t>704789</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1169030</t>
+          <t>1161420</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1297017</t>
+          <t>1295944</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>58702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90667</t>
+          <t>89114</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>89301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122872</t>
+          <t>123864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157839</t>
+          <t>157339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205913</t>
+          <t>203476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50644</t>
+          <t>49694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78199</t>
+          <t>78295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52139</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80024</t>
+          <t>82504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108953</t>
+          <t>109788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151114</t>
+          <t>149654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88920</t>
+          <t>85611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123222</t>
+          <t>123051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>63355</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>93054</t>
+          <t>92660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158751</t>
+          <t>155429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>208300</t>
+          <t>203619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69383</t>
+          <t>70357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102923</t>
+          <t>103449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54305</t>
+          <t>53305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85598</t>
+          <t>82754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131360</t>
+          <t>130224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174572</t>
+          <t>174751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73535</t>
+          <t>74269</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108838</t>
+          <t>107739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62969</t>
+          <t>64118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94976</t>
+          <t>98831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146731</t>
+          <t>146450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194358</t>
+          <t>193720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90231</t>
+          <t>87971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128289</t>
+          <t>127440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99708</t>
+          <t>99297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136602</t>
+          <t>137495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198560</t>
+          <t>198901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254654</t>
+          <t>252020</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91444</t>
+          <t>90808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131667</t>
+          <t>130584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83352</t>
+          <t>82602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117926</t>
+          <t>118431</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184999</t>
+          <t>186815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>235620</t>
+          <t>239260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122734</t>
+          <t>122490</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>163258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97172</t>
+          <t>98137</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134385</t>
+          <t>137092</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>230050</t>
+          <t>232176</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>285515</t>
+          <t>287143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104393</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142888</t>
+          <t>144080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97454</t>
+          <t>98217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134800</t>
+          <t>133945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211893</t>
+          <t>213426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265666</t>
+          <t>269431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85681</t>
+          <t>86370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>124126</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93205</t>
+          <t>93021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131115</t>
+          <t>130065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187069</t>
+          <t>188662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243112</t>
+          <t>240461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131743</t>
+          <t>132496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177742</t>
+          <t>175289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92620</t>
+          <t>92775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130323</t>
+          <t>128696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237794</t>
+          <t>239061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294991</t>
+          <t>294998</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111941</t>
+          <t>111939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>154223</t>
+          <t>154583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93889</t>
+          <t>92883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131955</t>
+          <t>131255</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214993</t>
+          <t>215729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273924</t>
+          <t>276467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123137</t>
+          <t>123018</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>165068</t>
+          <t>164569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>139390</t>
+          <t>138106</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183301</t>
+          <t>180978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>270935</t>
+          <t>271103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>330681</t>
+          <t>330736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>107050</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149105</t>
+          <t>148993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111714</t>
+          <t>112205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>151962</t>
+          <t>154235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>231943</t>
+          <t>231016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288385</t>
+          <t>289478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88542</t>
+          <t>87309</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126757</t>
+          <t>127275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121057</t>
+          <t>120870</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163832</t>
+          <t>166137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219828</t>
+          <t>218053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278437</t>
+          <t>276642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146401</t>
+          <t>144676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>192694</t>
+          <t>191697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150946</t>
+          <t>152043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199839</t>
+          <t>198380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>306800</t>
+          <t>309711</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374649</t>
+          <t>376242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116586</t>
+          <t>114116</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>158553</t>
+          <t>158248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102015</t>
+          <t>102532</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141625</t>
+          <t>142689</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227118</t>
+          <t>230944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>289164</t>
+          <t>288075</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103265</t>
+          <t>106122</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144814</t>
+          <t>147460</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>103299</t>
+          <t>103269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>146345</t>
+          <t>144367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>220032</t>
+          <t>221302</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>277024</t>
+          <t>280249</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>79275</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117017</t>
+          <t>113572</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96813</t>
+          <t>96515</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137607</t>
+          <t>137069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186136</t>
+          <t>188600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240720</t>
+          <t>242045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95825</t>
+          <t>94906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138996</t>
+          <t>138493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>91003</t>
+          <t>88677</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>131664</t>
+          <t>128335</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>196714</t>
+          <t>197855</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>254878</t>
+          <t>253665</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111558</t>
+          <t>111536</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>151165</t>
+          <t>149945</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>99462</t>
+          <t>98777</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138184</t>
+          <t>136893</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>219547</t>
+          <t>218305</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>276965</t>
+          <t>274403</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>73309</t>
+          <t>71310</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108559</t>
+          <t>106828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85938</t>
+          <t>84192</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122635</t>
+          <t>123606</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>166200</t>
+          <t>166898</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>217689</t>
+          <t>220553</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83393</t>
+          <t>85098</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>122291</t>
+          <t>121956</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>93300</t>
+          <t>91337</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>131271</t>
+          <t>130654</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>184857</t>
+          <t>187899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>237484</t>
+          <t>239262</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>65847</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100116</t>
+          <t>100126</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92312</t>
+          <t>90236</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>134513</t>
+          <t>132371</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>182639</t>
+          <t>180921</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>85756</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>74138</t>
+          <t>74752</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>109726</t>
+          <t>110347</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>136829</t>
+          <t>138512</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>186428</t>
+          <t>186733</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>88185</t>
+          <t>87402</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>121436</t>
+          <t>121472</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>82319</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115921</t>
+          <t>118080</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>176850</t>
+          <t>178162</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>225648</t>
+          <t>226593</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>50834</t>
+          <t>50743</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>79502</t>
+          <t>80481</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>86422</t>
+          <t>87478</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>113492</t>
+          <t>115048</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>155684</t>
+          <t>156554</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>45503</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74314</t>
+          <t>73532</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>65947</t>
+          <t>64646</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>98902</t>
+          <t>98468</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>118061</t>
+          <t>117053</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>161258</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>43375</t>
+          <t>44012</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>71421</t>
+          <t>71119</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>43938</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>73530</t>
+          <t>73794</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>96225</t>
+          <t>96810</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>135739</t>
+          <t>136332</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>37001</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>64133</t>
+          <t>65241</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>52239</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>83207</t>
+          <t>85027</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>100203</t>
+          <t>98889</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>138401</t>
+          <t>140169</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>73745</t>
+          <t>74987</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>102313</t>
+          <t>102626</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>91961</t>
+          <t>89200</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>131753</t>
+          <t>130855</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>173696</t>
+          <t>172736</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>221738</t>
+          <t>221781</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>31766</t>
+          <t>31328</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>51853</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>52834</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>84662</t>
+          <t>86580</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>89975</t>
+          <t>90043</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>130617</t>
+          <t>129526</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>37767</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>60202</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>63614</t>
+          <t>64093</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>100928</t>
+          <t>99366</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>109145</t>
+          <t>109893</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>152760</t>
+          <t>153046</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>27873</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>48455</t>
+          <t>48077</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>60641</t>
+          <t>60760</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>96353</t>
+          <t>97167</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>95370</t>
+          <t>93423</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>138174</t>
+          <t>134390</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>29984</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>51541</t>
+          <t>52122</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>77432</t>
+          <t>78798</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>81938</t>
+          <t>81524</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>121193</t>
+          <t>120042</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>776595</t>
+          <t>775157</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>876645</t>
+          <t>872957</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>783952</t>
+          <t>778738</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>884012</t>
+          <t>880635</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1593063</t>
+          <t>1581904</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1726593</t>
+          <t>1736188</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>591922</t>
+          <t>587945</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>683327</t>
+          <t>679092</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>590805</t>
+          <t>599802</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>686741</t>
+          <t>690104</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1211457</t>
+          <t>1208763</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1336381</t>
+          <t>1341339</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>672162</t>
+          <t>678100</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>770752</t>
+          <t>774882</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>699403</t>
+          <t>699012</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>796983</t>
+          <t>796669</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1398045</t>
+          <t>1403557</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1537869</t>
+          <t>1537875</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>563536</t>
+          <t>567732</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>655116</t>
+          <t>654526</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>593319</t>
+          <t>596082</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>685737</t>
+          <t>688363</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1188773</t>
+          <t>1185035</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1323789</t>
+          <t>1318546</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>531729</t>
+          <t>531216</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>622322</t>
+          <t>619386</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>609319</t>
+          <t>612804</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>704789</t>
+          <t>705048</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1161420</t>
+          <t>1168449</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1295944</t>
+          <t>1299154</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
